--- a/lesson_11/task.xlsx
+++ b/lesson_11/task.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Перший лист" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,74 +413,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ім'я</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Клас</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Вік</t>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Phone number</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Євген</t>
+          <t>234566</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0937265268</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Сашко</t>
+          <t>343647</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Jonh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Михайло</t>
+          <t>557554</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0664561024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>995735</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0730639565</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>234534</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0681989823</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4575675</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Olga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0976368593</t>
         </is>
       </c>
     </row>
